--- a/backend/data/orders.xlsx
+++ b/backend/data/orders.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -544,9 +544,38 @@
         <v>2026-09-29T09:53:05.496Z</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>8e636eff-6968-47bc-8bc9-c8463a55dd82</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v>guest</v>
+      </c>
+      <c r="D6" t="str">
+        <v>[{"productId":"3b610272-606d-4a05-a654-bd22d6633166","name":"candy biscuit","price":40,"quantity":1,"imageUrls":["/uploads/products/images/1790623968745-WhatsApp-Image-2026-09-18-at-7.53.49-AM.jpeg","/uploads/products/images/1790623968751-WhatsApp-Image-2026-09-19-at-3.45.16-AM.jpeg"]}]</v>
+      </c>
+      <c r="E6">
+        <v>40</v>
+      </c>
+      <c r="F6" t="str">
+        <v>{"name":"zakarya","line1":"i-14,rawlapindi","city":"rawalpindi","phone":"0334315352"}</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Cash on Delivery</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="I6" t="str">
+        <v>2026-09-30T15:04:52.829Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
   </ignoredErrors>
 </worksheet>
 </file>